--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/GEORGIA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/GEORGIA_2013.xlsx
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C137">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C191">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C316">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C763">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C877">
@@ -16908,7 +16908,7 @@
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C920">
@@ -17034,7 +17034,7 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C927">
@@ -24378,7 +24378,7 @@
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1335">
@@ -24900,7 +24900,7 @@
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1364">
@@ -27726,7 +27726,7 @@
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1521">
